--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484155_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484155_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1295</v>
+        <v>2.5337</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5581</v>
+        <v>2.9062</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4286</v>
+        <v>-0.3725</v>
       </c>
       <c r="G2" t="n">
         <v>-0.9301</v>
@@ -610,13 +610,13 @@
         <v>1.7855</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4682</v>
+        <v>-0.1275</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6349</v>
+        <v>-0.0169</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1667</v>
+        <v>-0.1106</v>
       </c>
       <c r="V2" t="n">
         <v>1.8059</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9919</v>
+        <v>2.2864</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0253</v>
+        <v>2.2917</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0334</v>
+        <v>-0.0054</v>
       </c>
       <c r="G3" t="n">
         <v>2.4995</v>
@@ -688,13 +688,13 @@
         <v>1.5871</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8882</v>
+        <v>-0.5937</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0485</v>
+        <v>-0.7821</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1603</v>
+        <v>0.1884</v>
       </c>
       <c r="V3" t="n">
         <v>-1.2065</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5865</v>
+        <v>2.0671</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6161</v>
+        <v>1.9845</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0296</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="G4" t="n">
         <v>2.1118</v>
@@ -766,13 +766,13 @@
         <v>0.9919</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.4613</v>
+        <v>-0.9806</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7877999999999999</v>
+        <v>-0.4194</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6735</v>
+        <v>-0.5613</v>
       </c>
       <c r="V4" t="n">
         <v>-0.056</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1227</v>
+        <v>0.2131</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9443</v>
+        <v>-0.8819</v>
       </c>
       <c r="F5" t="n">
-        <v>1.067</v>
+        <v>1.095</v>
       </c>
       <c r="G5" t="n">
         <v>-1.0438</v>
@@ -844,13 +844,13 @@
         <v>0.5952</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4404</v>
+        <v>-0.35</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4251</v>
+        <v>-0.3627</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0153</v>
+        <v>0.0127</v>
       </c>
       <c r="V5" t="n">
         <v>1.0118</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0373</v>
+        <v>0.1373</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9414</v>
+        <v>2.0037</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.9787</v>
+        <v>-1.8664</v>
       </c>
       <c r="G6" t="n">
         <v>0.539</v>
@@ -922,13 +922,13 @@
         <v>1.9838</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1551</v>
+        <v>-0.9806</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5894</v>
+        <v>-0.5271</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5657</v>
+        <v>-0.4535</v>
       </c>
       <c r="V6" t="n">
         <v>-1.405</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6263</v>
+        <v>-0.8227</v>
       </c>
       <c r="E7" t="n">
         <v>-1.09</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4637</v>
+        <v>0.2673</v>
       </c>
       <c r="G7" t="n">
         <v>-0.2049</v>
@@ -1000,13 +1000,13 @@
         <v>0.9919</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0289</v>
+        <v>-0.2253</v>
       </c>
       <c r="T7" t="n">
         <v>-0.289</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2601</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>0.5994</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7216</v>
+        <v>-1.1849</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2218</v>
+        <v>-0.8534</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4998</v>
+        <v>-0.3315</v>
       </c>
       <c r="G8" t="n">
         <v>-0.397</v>
@@ -1078,13 +1078,13 @@
         <v>1.1903</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8683999999999999</v>
+        <v>-0.3316</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4988</v>
+        <v>-0.1303</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3696</v>
+        <v>-0.2013</v>
       </c>
       <c r="V8" t="n">
         <v>0.3373</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9201</v>
+        <v>-1.8921</v>
       </c>
       <c r="E9" t="n">
         <v>-1.4454</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4747</v>
+        <v>-0.4467</v>
       </c>
       <c r="G9" t="n">
         <v>-0.081</v>
@@ -1156,13 +1156,13 @@
         <v>0.7935</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1683</v>
+        <v>-0.1403</v>
       </c>
       <c r="T9" t="n">
         <v>-0.4988</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3304</v>
+        <v>0.3585</v>
       </c>
       <c r="V9" t="n">
         <v>-1.4724</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. AMABILINO PEREZ</t>
+          <t>R. SOLIVELLES MENDEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0788</v>
+        <v>-2.0289</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2797</v>
+        <v>-0.1638</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7992</v>
+        <v>-1.8651</v>
       </c>
       <c r="G10" t="n">
-        <v>1.0201</v>
+        <v>0.3529</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.5217</v>
+        <v>0.66</v>
       </c>
       <c r="I10" t="n">
-        <v>2.5418</v>
+        <v>-0.3071</v>
       </c>
       <c r="J10" t="n">
-        <v>1.7908</v>
+        <v>0.2727</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.9493</v>
+        <v>0.9879</v>
       </c>
       <c r="L10" t="n">
-        <v>3.7401</v>
+        <v>-0.7153</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7707000000000001</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4277</v>
+        <v>-0.3279</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1983</v>
+        <v>0.4081</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.1822</v>
+        <v>0.3968</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.9677</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7855</v>
+        <v>0.3968</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3135</v>
+        <v>-0.3656</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9125</v>
+        <v>-0.4364</v>
       </c>
       <c r="U10" t="n">
-        <v>0.599</v>
+        <v>0.0708</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6032</v>
+        <v>-2.4129</v>
       </c>
       <c r="W10" t="n">
-        <v>1.8097</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>-2.4129</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. SOLIVELLES MENDEZ</t>
+          <t>A. AMABILINO PEREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1972</v>
+        <v>-2.1834</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1638</v>
+        <v>-1.0756</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0334</v>
+        <v>-1.1078</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3529</v>
+        <v>1.0201</v>
       </c>
       <c r="H11" t="n">
-        <v>0.66</v>
+        <v>-1.5217</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3071</v>
+        <v>2.5418</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2727</v>
+        <v>1.7908</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9879</v>
+        <v>-1.9493</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7153</v>
+        <v>3.7401</v>
       </c>
       <c r="M11" t="n">
-        <v>0.08019999999999999</v>
+        <v>-0.7707000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3279</v>
+        <v>0.4277</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4081</v>
+        <v>-1.1983</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3968</v>
+        <v>-2.1822</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-3.9677</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3968</v>
+        <v>1.7855</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5339</v>
+        <v>-0.418</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4364</v>
+        <v>-0.7084</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0975</v>
+        <v>0.2904</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.4129</v>
+        <v>-0.6032</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.8097</v>
       </c>
       <c r="X11" t="n">
         <v>-2.4129</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6395</v>
+        <v>-2.4204</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9937</v>
+        <v>-2.971</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3542</v>
+        <v>0.5505</v>
       </c>
       <c r="G12" t="n">
         <v>-0.9004</v>
@@ -1390,13 +1390,13 @@
         <v>1.5871</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0763</v>
+        <v>-0.8573</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8047</v>
+        <v>-0.7821</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2716</v>
+        <v>-0.0752</v>
       </c>
       <c r="V12" t="n">
         <v>-0.266</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.9134</v>
+        <v>-3.3855</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.4037</v>
+        <v>-0.483</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.5097</v>
+        <v>-2.9025</v>
       </c>
       <c r="G13" t="n">
         <v>-2.0636</v>
@@ -1468,13 +1468,13 @@
         <v>1.1903</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5713</v>
+        <v>0.0992</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1304</v>
+        <v>0.0511</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4409</v>
+        <v>0.0481</v>
       </c>
       <c r="V13" t="n">
         <v>-2.6115</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-7.3036</v>
+        <v>-6.6803</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.4015000000000002</v>
+        <v>0.2220000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.902200000000001</v>
+        <v>-6.9025</v>
       </c>
       <c r="G14" t="n">
         <v>0.9025000000000003</v>
@@ -1546,13 +1546,13 @@
         <v>14.8789</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.8948</v>
+        <v>-5.2713</v>
       </c>
       <c r="T14" t="n">
-        <v>-5.525700000000001</v>
+        <v>-4.9021</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3691999999999998</v>
+        <v>-0.3693000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-6.2791</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. BUSCAIL BRIANSO</t>
+          <t>D. FERNANDEZ LINARES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.6641</v>
+        <v>4.7116</v>
       </c>
       <c r="E15" t="n">
-        <v>4.344</v>
+        <v>4.0128</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3201</v>
+        <v>0.6988</v>
       </c>
       <c r="G15" t="n">
-        <v>2.713</v>
+        <v>0.1928</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5911</v>
+        <v>-1.9306</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1219</v>
+        <v>2.1235</v>
       </c>
       <c r="J15" t="n">
-        <v>4.0706</v>
+        <v>1.4144</v>
       </c>
       <c r="K15" t="n">
-        <v>3.3075</v>
+        <v>-1.0781</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7631</v>
+        <v>2.4926</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3576</v>
+        <v>-1.2216</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7165</v>
+        <v>-0.8525</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6412</v>
+        <v>-0.3691</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.1903</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9758</v>
+        <v>-1.9838</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7855</v>
+        <v>1.1903</v>
       </c>
       <c r="S15" t="n">
-        <v>3.2127</v>
+        <v>1.0897</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8479</v>
+        <v>-0.2436</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3647</v>
+        <v>1.3333</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.0713</v>
+        <v>4.2226</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4012</v>
+        <v>4.8259</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.4724</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ LINARES</t>
+          <t>M. BUSCAIL BRIANSO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.8197</v>
+        <v>3.319</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1966</v>
+        <v>3.1196</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6231</v>
+        <v>0.1994</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1928</v>
+        <v>2.713</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.9306</v>
+        <v>2.5911</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1235</v>
+        <v>0.1219</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4144</v>
+        <v>4.0706</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.0781</v>
+        <v>3.3075</v>
       </c>
       <c r="L16" t="n">
-        <v>2.4926</v>
+        <v>0.7631</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2216</v>
+        <v>-1.3576</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8525</v>
+        <v>-0.7165</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3691</v>
+        <v>-0.6412</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.7935</v>
+        <v>-1.1903</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9838</v>
+        <v>-2.9758</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1903</v>
+        <v>1.7855</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1978</v>
+        <v>1.8676</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0599</v>
+        <v>0.6236</v>
       </c>
       <c r="U16" t="n">
-        <v>1.2576</v>
+        <v>1.244</v>
       </c>
       <c r="V16" t="n">
-        <v>4.2226</v>
+        <v>-0.0713</v>
       </c>
       <c r="W16" t="n">
-        <v>4.8259</v>
+        <v>1.4012</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6032</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. LORAS MONTERO</t>
+          <t>M. ISSOUF</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.6814</v>
+        <v>1.9057</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5568</v>
+        <v>2.4579</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1246</v>
+        <v>-0.5522</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2956</v>
+        <v>1.8037</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7356</v>
+        <v>2.3284</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0312</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3867</v>
+        <v>2.5202</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3816</v>
+        <v>2.5202</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0051</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6823</v>
+        <v>-0.7165</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.646</v>
+        <v>-0.1918</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0363</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.1822</v>
+        <v>0.1984</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.9677</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7855</v>
+        <v>0.1984</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1548</v>
+        <v>-0.0964</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8673999999999999</v>
+        <v>-0.0623</v>
       </c>
       <c r="U17" t="n">
-        <v>2.2874</v>
+        <v>-0.034</v>
       </c>
       <c r="V17" t="n">
-        <v>2.0044</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.2704</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. ISSOUF</t>
+          <t>D. LORAS MONTERO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.2118</v>
+        <v>1.6918</v>
       </c>
       <c r="E18" t="n">
-        <v>2.764</v>
+        <v>-0.0554</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5522</v>
+        <v>1.7472</v>
       </c>
       <c r="G18" t="n">
-        <v>1.8037</v>
+        <v>-0.2956</v>
       </c>
       <c r="H18" t="n">
-        <v>2.3284</v>
+        <v>0.7356</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-1.0312</v>
       </c>
       <c r="J18" t="n">
-        <v>2.5202</v>
+        <v>1.3867</v>
       </c>
       <c r="K18" t="n">
-        <v>2.5202</v>
+        <v>1.3816</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.0051</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7165</v>
+        <v>-1.6823</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1918</v>
+        <v>-0.646</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-1.0363</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1984</v>
+        <v>-2.1822</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-3.9677</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1984</v>
+        <v>1.7855</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2097</v>
+        <v>2.1652</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2438</v>
+        <v>0.2552</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.034</v>
+        <v>1.91</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>2.0044</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.2704</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6528</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6512</v>
+        <v>-0.4471</v>
       </c>
       <c r="F19" t="n">
-        <v>1.304</v>
+        <v>1.3881</v>
       </c>
       <c r="G19" t="n">
         <v>0.0128</v>
@@ -1936,13 +1936,13 @@
         <v>0.9919</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.352</v>
+        <v>-0.0638</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3741</v>
+        <v>-0.17</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0221</v>
+        <v>0.1062</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. LOPEZ SAURA</t>
+          <t>A. SENGHOR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1661</v>
+        <v>0.2909</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1247</v>
+        <v>-0.4413</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2908</v>
+        <v>0.7322</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2721</v>
+        <v>-0.7498</v>
       </c>
       <c r="H20" t="n">
-        <v>0.136</v>
+        <v>-0.8366</v>
       </c>
       <c r="I20" t="n">
-        <v>0.136</v>
+        <v>0.0868</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.5595</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>-0.6399</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.0803</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2721</v>
+        <v>-0.1902</v>
       </c>
       <c r="N20" t="n">
-        <v>0.136</v>
+        <v>-0.1967</v>
       </c>
       <c r="O20" t="n">
-        <v>0.136</v>
+        <v>0.0065</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.5952</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.106</v>
+        <v>0.231</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1247</v>
+        <v>-0.0963</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0187</v>
+        <v>0.3273</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. SENGHOR</t>
+          <t>M. LOPEZ SAURA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1095</v>
+        <v>0.1941</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6454</v>
+        <v>-0.1247</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5358000000000001</v>
+        <v>0.3188</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7498</v>
+        <v>0.2721</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8366</v>
+        <v>0.136</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0868</v>
+        <v>0.136</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5595</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6399</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0803</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1902</v>
+        <v>0.2721</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1967</v>
+        <v>0.136</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0065</v>
+        <v>0.136</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3968</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5952</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1695</v>
+        <v>-0.0779</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3004</v>
+        <v>-0.1247</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1309</v>
+        <v>0.0468</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. FERNANDEZ MASIP</t>
+          <t>D. FERNANDEZ STEFANUTO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9681999999999999</v>
+        <v>-0.2172</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9644</v>
+        <v>-0.489</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0038</v>
+        <v>0.2718</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.3706</v>
+        <v>-1.8288</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.083</v>
+        <v>-2.0557</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2876</v>
+        <v>0.2268</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3951</v>
+        <v>-0.6891</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.0945</v>
+        <v>-1.4145</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4896</v>
+        <v>0.7255</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.7658</v>
+        <v>-1.1398</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9885</v>
+        <v>-0.6411</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7772</v>
+        <v>-0.4986</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.7855</v>
+        <v>1.1903</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9758</v>
+        <v>-0.9919</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1903</v>
+        <v>2.1822</v>
       </c>
       <c r="S22" t="n">
-        <v>1.4613</v>
+        <v>1.0245</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6236</v>
+        <v>0.0568</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8377</v>
+        <v>0.9677</v>
       </c>
       <c r="V22" t="n">
-        <v>0.7267</v>
+        <v>-0.6032</v>
       </c>
       <c r="W22" t="n">
-        <v>0.9926</v>
+        <v>1.1352</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.266</v>
+        <v>-1.7384</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. BLÁZQUEZ FARRIOL</t>
+          <t>I. FERNANDEZ MASIP</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.3433</v>
+        <v>-0.8679</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.223</v>
+        <v>-1.1685</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1203</v>
+        <v>0.3006</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.3752</v>
+        <v>-1.3706</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2521</v>
+        <v>-1.083</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.123</v>
+        <v>-0.2876</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0806</v>
+        <v>0.3951</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0806</v>
+        <v>-0.0945</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>0.4896</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.4558</v>
+        <v>-1.7658</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3328</v>
+        <v>-0.9885</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.123</v>
+        <v>-0.7772</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.5952</v>
+        <v>-1.7855</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9919</v>
+        <v>-2.9758</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3968</v>
+        <v>1.1903</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.373</v>
+        <v>1.5616</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3117</v>
+        <v>0.4195</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0612</v>
+        <v>1.142</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.7267</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.9926</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ STEFANUTO</t>
+          <t>A. BLÁZQUEZ FARRIOL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.8828</v>
+        <v>-0.8909</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.1012</v>
+        <v>-1.0189</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7816</v>
+        <v>0.128</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.8288</v>
+        <v>-0.3752</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.0557</v>
+        <v>-0.2521</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2268</v>
+        <v>-0.123</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6891</v>
+        <v>0.0806</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.4145</v>
+        <v>0.0806</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7255</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.1398</v>
+        <v>-0.4558</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6411</v>
+        <v>-0.3328</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.4986</v>
+        <v>-0.123</v>
       </c>
       <c r="P24" t="n">
-        <v>1.1903</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q24" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R24" t="n">
-        <v>2.1822</v>
+        <v>0.3968</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.641</v>
+        <v>0.0794</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5554</v>
+        <v>-0.1077</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0857</v>
+        <v>0.187</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1352</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.7384</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.5882</v>
+        <v>-1.7337</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7509</v>
+        <v>1.057</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.3391</v>
+        <v>-2.7907</v>
       </c>
       <c r="G25" t="n">
         <v>-1.2769</v>
@@ -2404,13 +2404,13 @@
         <v>0.5952</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7</v>
+        <v>0.1545</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4874</v>
+        <v>-0.1813</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2126</v>
+        <v>0.3358</v>
       </c>
       <c r="V25" t="n">
         <v>-1.2065</v>
@@ -2437,34 +2437,34 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>7.303900000000002</v>
+        <v>9.344399999999998</v>
       </c>
       <c r="E26" t="n">
         <v>6.9024</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4013999999999998</v>
+        <v>2.442</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.9025000000000001</v>
+        <v>-0.9024999999999999</v>
       </c>
       <c r="H26" t="n">
         <v>-1.0324</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1301000000000003</v>
+        <v>0.1301000000000002</v>
       </c>
       <c r="J26" t="n">
-        <v>8.107800000000001</v>
+        <v>8.107799999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>3.508999999999999</v>
+        <v>3.509000000000001</v>
       </c>
       <c r="L26" t="n">
         <v>4.5989</v>
       </c>
       <c r="M26" t="n">
-        <v>-9.010300000000001</v>
+        <v>-9.010299999999999</v>
       </c>
       <c r="N26" t="n">
         <v>-4.5415</v>
@@ -2473,7 +2473,7 @@
         <v>-4.4688</v>
       </c>
       <c r="P26" t="n">
-        <v>-3.967700000000001</v>
+        <v>-3.9677</v>
       </c>
       <c r="Q26" t="n">
         <v>-14.8788</v>
@@ -2482,13 +2482,13 @@
         <v>10.9113</v>
       </c>
       <c r="S26" t="n">
-        <v>5.894799999999999</v>
+        <v>7.935399999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>0.3691000000000002</v>
+        <v>0.3691999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>5.5256</v>
+        <v>7.5661</v>
       </c>
       <c r="V26" t="n">
         <v>6.279199999999999</v>
